--- a/reports/集团总公司_现金流量表_2025-05.xlsx
+++ b/reports/集团总公司_现金流量表_2025-05.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>200850000</v>
+        <v>201424939</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>934050000</v>
+        <v>932854811</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4112871</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>19224091</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2074564</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>9595345</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1027208</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>4802353</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>829791</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>3841465</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>616979</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2878881</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>414086</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1922265</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>309314</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1438527</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>206405</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>961519</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>517168</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>2397232</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>258565</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>1207876</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>164828</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>762521</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>545900</v>
+        <v>543229</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>2538700</v>
+        <v>2540137</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3708000</v>
+        <v>3726408</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>17244000</v>
+        <v>17241712</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>205103900</v>
+        <v>216226355</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>123600000</v>
+        <v>123706002</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>574800000</v>
+        <v>574004058</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1373210</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>6409879</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1036149</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>4795550</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>685110</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3203323</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>518752</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>2399478</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>342446</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1600317</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>260522</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>1206958</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24926000</v>
+        <v>24846115</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>115918000</v>
+        <v>115819509</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11536000</v>
+        <v>11556912</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>53648000</v>
+        <v>53709947</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5253000</v>
+        <v>5251787</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>24429000</v>
+        <v>24396292</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>165315000</v>
+        <v>169577005</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>39788900</v>
+        <v>46649350</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>239049</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>1200000</v>
+        <v>1199584</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2097252</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>10500000</v>
+        <v>10488904</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1279616</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>6400000</v>
+        <v>6408088</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2336301</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>19934853</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>100000000</v>
+        <v>100127269</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2912463</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>14500000</v>
+        <v>14484423</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14130585</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>71000000</v>
+        <v>71054214</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>518792</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>2600000</v>
+        <v>2597781</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20453645</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18117344</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4717113</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>23500000</v>
+        <v>23471291</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7537291</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>37500000</v>
+        <v>37475893</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7463397</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>37500000</v>
+        <v>37508801</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>241027</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>1200000</v>
+        <v>1200238</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12495431</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6111234</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>30500000</v>
+        <v>30529221</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6098402</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>30500000</v>
+        <v>30463217</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>998655</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>5000000</v>
+        <v>5006640</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>866535</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>4350000</v>
+        <v>4355034</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>125593</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>625000</v>
+        <v>624450</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7235482</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5259949</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>26823900</v>
+        <v>33791955</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>26823900</v>
+        <v>33791955</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
